--- a/Lab Applied Statistics/codebook_mensa.xlsx
+++ b/Lab Applied Statistics/codebook_mensa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alumnisssup-my.sharepoint.com/personal/valentina_lorenzoni_santannapisa_it/Documents/Laboratorio_Stat_Appl/Practicum1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="126" documentId="8_{0E2A34CB-48DC-4651-9C17-6917FFC11329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F2A46C8-CEB1-4416-842B-1332DFF8B1D9}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="8_{0E2A34CB-48DC-4651-9C17-6917FFC11329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C8695DB-0BA3-4AA9-8E70-EB1F07208870}"/>
   <bookViews>
-    <workbookView xWindow="792" yWindow="6264" windowWidth="17016" windowHeight="5568" xr2:uid="{40D6FB52-6A16-42CD-8214-62586EDF60AF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{40D6FB52-6A16-42CD-8214-62586EDF60AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="59">
   <si>
     <t>Variable name</t>
   </si>
@@ -204,6 +204,15 @@
   </si>
   <si>
     <t>Study department</t>
+  </si>
+  <si>
+    <t>tariff_code</t>
+  </si>
+  <si>
+    <t>1=Full tariff, 2=Meal for free (resident), 3=Meal for free (not resident), 5=Full tariff (foreign), 6=Reduced tariff</t>
+  </si>
+  <si>
+    <t>Type of tariff (mensa_esercitazione2.dta)</t>
   </si>
 </sst>
 </file>
@@ -587,7 +596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20106320-AD95-4124-9C6D-12954A97DA5C}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.5546875" customWidth="1"/>
@@ -853,6 +862,20 @@
         <v>19</v>
       </c>
     </row>
+    <row r="21" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
